--- a/reports/pdf_rolling5_20260930.xlsx
+++ b/reports/pdf_rolling5_20260930.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,977억   ·   현금 42억(0.8%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 16종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,977억   ·   현금 21억(0.4%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 16종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1221,88 +1221,88 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>223859973</v>
+        <v>1030739874</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>4.58%→5.18%</t>
+          <t>1.77%→2.04%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-620313524</v>
+        <v>-301103963</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.68%→0.49%</t>
+          <t>1.07%→0.93%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1030739874</v>
+        <v>223859973</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.77%→2.04%</t>
+          <t>4.58%→5.18%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-301103963</v>
+        <v>-620313524</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.93%</t>
+          <t>0.68%→0.49%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,259억   ·   현금 76억(2.3%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 3종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,259억   ·   현금 38억(1.2%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1614,7 +1614,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,697억   ·   현금 86억(3.1%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,697억   ·   현금 43억(1.6%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1638,7 +1638,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 22억(1.1%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 6종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 11억(0.5%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1991,7 +1991,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 305억   ·   현금 3억(0.9%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 10종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 305억   ·   현금 1억(0.5%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2453,23 +2453,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-54725969</v>
+        <v>-63923963</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.34%→2.16%</t>
+          <t>2.84%→2.63%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2525,23 +2525,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-63923963</v>
+        <v>-35111980</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.63%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2553,30 +2553,30 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-35111980</v>
+        <v>-54725969</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>2.34%→2.16%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 15억(3.1%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 1종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 8억(1.6%)      오늘 2026-09-30  vs  5일전 2026-09-21      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260930.xlsx
+++ b/reports/pdf_rolling5_20260930.xlsx
@@ -2432,88 +2432,88 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>64875963</v>
+        <v>88591949</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.18%→0.40%</t>
+          <t>2.79%→3.08%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-63923963</v>
+        <v>-54725969</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.63%</t>
+          <t>2.34%→2.16%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>88591949</v>
+        <v>64875963</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.79%→3.08%</t>
+          <t>0.18%→0.40%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-71735959</v>
+        <v>-63923963</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.83%</t>
+          <t>2.84%→2.63%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2525,23 +2525,23 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-35111980</v>
+        <v>-71735959</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>3.07%→2.83%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2553,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-54725969</v>
+        <v>-35111980</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.34%→2.16%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260930.xlsx
+++ b/reports/pdf_rolling5_20260930.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,13 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -162,6 +172,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-21 ~ 2026-09-30  (최근 5거래일)  ·  캡처 7/7</t>
+          <t>최근 5거래일 변화  ·  2026-09-21 ~ 2026-09-30  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2743883665</v>
+        <v>-860507895</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.67%→1.91%</t>
+          <t>0.73%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1198,111 +1212,111 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-860507895</v>
+        <v>-2743883665</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.47%</t>
+          <t>2.67%→1.91%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1030739874</v>
+        <v>223859973</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.77%→2.04%</t>
+          <t>4.58%→5.18%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-301103963</v>
+        <v>-620313524</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.93%</t>
+          <t>0.68%→0.49%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>223859973</v>
+        <v>1030739874</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>4.58%→5.18%</t>
+          <t>1.77%→2.04%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-620313524</v>
+        <v>-301103963</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.68%→0.49%</t>
+          <t>1.07%→0.93%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -2453,18 +2467,18 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-54725969</v>
+        <v>-71735959</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.34%→2.16%</t>
+          <t>3.07%→2.83%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2525,18 +2539,18 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-71735959</v>
+        <v>-54725969</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.83%</t>
+          <t>2.34%→2.16%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2735,31 +2749,24 @@
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,141억      오늘 2026-09-30  vs  5일전 2026-09-21      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="20" t="n"/>
+      <c r="J67" s="20" t="n"/>
+      <c r="K67" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="G36:K36"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A45:K45"/>
@@ -2778,7 +2785,6 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A68:K68"/>
     <mergeCell ref="G46:K46"/>
     <mergeCell ref="A67:K67"/>
   </mergeCells>

--- a/reports/pdf_rolling5_20260930.xlsx
+++ b/reports/pdf_rolling5_20260930.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,13 +62,8 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -100,11 +95,6 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,10 +162,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-21 ~ 2026-09-30  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-21 ~ 2026-09-30  (최근 5거래일)  ·  캡처 7/7</t>
         </is>
       </c>
     </row>
@@ -1168,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-860507895</v>
+        <v>-2743883665</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.47%</t>
+          <t>2.67%→1.91%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1212,46 +1198,46 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2743883665</v>
+        <v>-860507895</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>2.67%→1.91%</t>
+          <t>0.73%→0.47%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>223859973</v>
+        <v>1030739874</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>4.58%→5.18%</t>
+          <t>1.77%→2.04%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1279,23 +1265,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1030739874</v>
+        <v>223859973</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.77%→2.04%</t>
+          <t>4.58%→5.18%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2335,23 +2321,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-17471990</v>
+        <v>-19865989</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.95%→3.89%</t>
+          <t>0.49%→0.42%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>824→812</t>
+          <t>89→77</t>
         </is>
       </c>
     </row>
@@ -2379,23 +2365,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-19865989</v>
+        <v>-17471990</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.42%</t>
+          <t>3.95%→3.89%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>89→77</t>
+          <t>824→812</t>
         </is>
       </c>
     </row>
@@ -2446,88 +2432,88 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>88591949</v>
+        <v>64875963</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.79%→3.08%</t>
+          <t>0.18%→0.40%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>67→74</t>
+          <t>6→13</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-71735959</v>
+        <v>-35111980</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.83%</t>
+          <t>1.54%→1.42%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>64875963</v>
+        <v>88591949</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.18%→0.40%</t>
+          <t>2.79%→3.08%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>6→13</t>
+          <t>67→74</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-63923963</v>
+        <v>-71735959</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.63%</t>
+          <t>3.07%→2.83%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2567,23 +2553,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-35111980</v>
+        <v>-63923963</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.42%</t>
+          <t>2.84%→2.63%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2749,24 +2735,31 @@
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="20" t="n"/>
-      <c r="G67" s="20" t="n"/>
-      <c r="H67" s="20" t="n"/>
-      <c r="I67" s="20" t="n"/>
-      <c r="J67" s="20" t="n"/>
-      <c r="K67" s="20" t="n"/>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,141억      오늘 2026-09-30  vs  5일전 2026-09-21      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="G36:K36"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A45:K45"/>
@@ -2785,6 +2778,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:K68"/>
     <mergeCell ref="G46:K46"/>
     <mergeCell ref="A67:K67"/>
   </mergeCells>
